--- a/StructureDefinition-FoodAllergyModel.xlsx
+++ b/StructureDefinition-FoodAllergyModel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-27T22:35:49+00:00</t>
+    <t>2022-02-27T22:48:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-FoodAllergyModel.xlsx
+++ b/StructureDefinition-FoodAllergyModel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-27T22:48:25+00:00</t>
+    <t>2022-02-27T22:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-FoodAllergyModel.xlsx
+++ b/StructureDefinition-FoodAllergyModel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-27T22:59:15+00:00</t>
+    <t>2022-02-27T23:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
